--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1310,4 +1311,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-16 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1888</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>3457</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>460</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>5310</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9767</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+2052</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>5640</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5483</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>9939</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2460</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4342</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4779</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>25992</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>33433</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2880</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>37828</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2577</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>8208</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+2580</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>22445</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>531</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>33494</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2589</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>47068</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2748</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16602</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>17125</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>18768</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+270</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>54984</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1694</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>907</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>26228</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2547</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4352</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -1337,7 +1337,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-16 13:01:00</t>
+          <t>Timestamp: 2026-07-16 13:31:00</t>
         </is>
       </c>
     </row>
@@ -1620,11 +1620,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>9939</v>
+        <v>9999</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+2460</t>
+          <t>+2520</t>
         </is>
       </c>
     </row>
@@ -1770,11 +1770,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>33433</v>
+        <v>33493</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2880</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -1845,11 +1845,11 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>8208</v>
+        <v>8268</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>+2580</t>
+          <t>+2640</t>
         </is>
       </c>
     </row>
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>33494</v>
+        <v>33554</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+2589</t>
+          <t>+2649</t>
         </is>
       </c>
     </row>
@@ -2010,11 +2010,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>47068</v>
+        <v>47128</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+2748</t>
+          <t>+2808</t>
         </is>
       </c>
     </row>
@@ -2070,11 +2070,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>54984</v>
+        <v>55035</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+1694</t>
+          <t>+1745</t>
         </is>
       </c>
     </row>
@@ -2130,11 +2130,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>26228</v>
+        <v>26339</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2547</t>
+          <t>+2658</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -2217,7 +2217,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-17 13:01:00</t>
+          <t>Timestamp: 2026-07-17 13:31:00</t>
         </is>
       </c>
     </row>
@@ -2350,11 +2350,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>11480</v>
+        <v>11740</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+1713</t>
+          <t>+1973</t>
         </is>
       </c>
     </row>
@@ -2695,11 +2695,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>40591</v>
+        <v>40651</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+2763</t>
+          <t>+2823</t>
         </is>
       </c>
     </row>
@@ -2890,11 +2890,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>49786</v>
+        <v>49846</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+2658</t>
+          <t>+2718</t>
         </is>
       </c>
     </row>
@@ -2950,11 +2950,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>57552</v>
+        <v>57612</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2517</t>
+          <t>+2577</t>
         </is>
       </c>
     </row>
@@ -3010,11 +3010,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>28256</v>
+        <v>28316</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+1917</t>
+          <t>+1977</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -10,6 +10,7 @@
     <sheet name="2026-07-15" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3070,4 +3071,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-18 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>11810</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+7183</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>11395</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+5903</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>4382</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>483</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>7765</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+5845</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>6525</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>704</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>11740</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2835</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+1935</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>5640</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>5483</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+922</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>12183</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+70</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+1530</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4342</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>9521</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+3322</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+1910</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>29918</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+2776</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>40651</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+4253</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2936</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+2856</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43354</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2703</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>13950</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+2871</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>22755</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+310</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>2793</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1962</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>37489</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+2495</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>52351</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2505</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>16902</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>17125</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>20136</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>60423</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2811</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1357</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+450</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>30173</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1857</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>421</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4352</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -11,6 +11,7 @@
     <sheet name="2026-07-16" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3950,4 +3951,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-19 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>35040</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+23230</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>33103</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+21708</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>33911</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+29529</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>28977</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+28494</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>28096</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+20331</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>26056</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+19531</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>20865</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+20161</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>40093</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+28353</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>22608</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+22588</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>15356</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+15356</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>23965</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+23965</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>19924</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+19674</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37262</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+34427</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>29445</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+23805</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>21948</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+16465</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>29659</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+28636</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>27709</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+27709</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>35906</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+23723</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>18678</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+18528</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>23972</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+23972</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>32450</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+32450</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>28488</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+28418</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>29735</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+27725</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>31277</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+26935</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>37844</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+28323</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>34481</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+32541</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>60367</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+30449</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>70069</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+29298</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>32042</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+29106</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>15897</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+15897</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>72310</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+28836</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>32054</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+32054</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>51665</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+37715</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>18864</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+18854</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>35625</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+12750</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>25007</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+25007</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>19730</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+19730</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>26042</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+23129</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>24340</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+24340</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>26258</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+25358</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>25869</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+25869</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>26740</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+26740</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>66848</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+29298</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>85790</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+33279</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>47198</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+30176</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>45879</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+28754</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>45848</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+25712</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>92307</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+31764</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>25226</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+24951</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>26815</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+25458</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>24293</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+24293</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>58170</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+27997</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>20697</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+20697</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>23673</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+23252</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>26403</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+22051</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -3977,7 +3977,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-19 13:01:00</t>
+          <t>Timestamp: 2026-07-19 13:31:00</t>
         </is>
       </c>
     </row>
@@ -4005,11 +4005,11 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>35040</v>
+        <v>0</v>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>+23230</t>
+          <t>-11810</t>
         </is>
       </c>
     </row>
@@ -4020,11 +4020,11 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>33103</v>
+        <v>0</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+21708</t>
+          <t>-11395</t>
         </is>
       </c>
     </row>
@@ -4035,11 +4035,11 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>33911</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+29529</t>
+          <t>-4382</t>
         </is>
       </c>
     </row>
@@ -4050,11 +4050,11 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>28977</v>
+        <v>0</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>+28494</t>
+          <t>-483</t>
         </is>
       </c>
     </row>
@@ -4065,11 +4065,11 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>28096</v>
+        <v>0</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+20331</t>
+          <t>-7765</t>
         </is>
       </c>
     </row>
@@ -4080,11 +4080,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>26056</v>
+        <v>0</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+19531</t>
+          <t>-6525</t>
         </is>
       </c>
     </row>
@@ -4095,11 +4095,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>20865</v>
+        <v>0</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+20161</t>
+          <t>-704</t>
         </is>
       </c>
     </row>
@@ -4110,11 +4110,11 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>40093</v>
+        <v>0</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+28353</t>
+          <t>-11740</t>
         </is>
       </c>
     </row>
@@ -4125,11 +4125,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>22608</v>
+        <v>0</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+22588</t>
+          <t>-20</t>
         </is>
       </c>
     </row>
@@ -4140,11 +4140,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>15356</v>
+        <v>0</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+15356</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4155,11 +4155,11 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>23965</v>
+        <v>0</v>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>+23965</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4170,11 +4170,11 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>19924</v>
+        <v>0</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>+19674</t>
+          <t>-250</t>
         </is>
       </c>
     </row>
@@ -4185,11 +4185,11 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>37262</v>
+        <v>0</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>+34427</t>
+          <t>-2835</t>
         </is>
       </c>
     </row>
@@ -4200,11 +4200,11 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>29445</v>
+        <v>0</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+23805</t>
+          <t>-5640</t>
         </is>
       </c>
     </row>
@@ -4215,11 +4215,11 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>21948</v>
+        <v>0</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>+16465</t>
+          <t>-5483</t>
         </is>
       </c>
     </row>
@@ -4230,11 +4230,11 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>29659</v>
+        <v>0</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>+28636</t>
+          <t>-1023</t>
         </is>
       </c>
     </row>
@@ -4245,11 +4245,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>27709</v>
+        <v>0</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+27709</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4260,11 +4260,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>35906</v>
+        <v>0</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+23723</t>
+          <t>-12183</t>
         </is>
       </c>
     </row>
@@ -4275,11 +4275,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>18678</v>
+        <v>0</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>+18528</t>
+          <t>-150</t>
         </is>
       </c>
     </row>
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>23972</v>
+        <v>0</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>+23972</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4305,11 +4305,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>32450</v>
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>+32450</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4320,11 +4320,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>28488</v>
+        <v>0</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>+28418</t>
+          <t>-70</t>
         </is>
       </c>
     </row>
@@ -4335,11 +4335,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>29735</v>
+        <v>0</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+27725</t>
+          <t>-2010</t>
         </is>
       </c>
     </row>
@@ -4350,11 +4350,11 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>31277</v>
+        <v>0</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>+26935</t>
+          <t>-4342</t>
         </is>
       </c>
     </row>
@@ -4365,11 +4365,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>37844</v>
+        <v>0</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>+28323</t>
+          <t>-9521</t>
         </is>
       </c>
     </row>
@@ -4380,11 +4380,11 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>34481</v>
+        <v>0</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>+32541</t>
+          <t>-1940</t>
         </is>
       </c>
     </row>
@@ -4395,11 +4395,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>60367</v>
+        <v>0</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+30449</t>
+          <t>-29918</t>
         </is>
       </c>
     </row>
@@ -4410,11 +4410,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>70069</v>
+        <v>0</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+29298</t>
+          <t>-40771</t>
         </is>
       </c>
     </row>
@@ -4425,11 +4425,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>32042</v>
+        <v>0</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>+29106</t>
+          <t>-2936</t>
         </is>
       </c>
     </row>
@@ -4440,11 +4440,11 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>15897</v>
+        <v>0</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>+15897</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4455,11 +4455,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>72310</v>
+        <v>0</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+28836</t>
+          <t>-43474</t>
         </is>
       </c>
     </row>
@@ -4470,11 +4470,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>32054</v>
+        <v>0</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+32054</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4485,11 +4485,11 @@
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>51665</v>
+        <v>0</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>+37715</t>
+          <t>-13950</t>
         </is>
       </c>
     </row>
@@ -4500,11 +4500,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>18864</v>
+        <v>0</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+18854</t>
+          <t>-10</t>
         </is>
       </c>
     </row>
@@ -4515,11 +4515,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>35625</v>
+        <v>0</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+12750</t>
+          <t>-22875</t>
         </is>
       </c>
     </row>
@@ -4530,11 +4530,11 @@
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>25007</v>
+        <v>0</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>+25007</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4545,11 +4545,11 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>19730</v>
+        <v>0</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+19730</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>26042</v>
+        <v>0</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+23129</t>
+          <t>-2913</t>
         </is>
       </c>
     </row>
@@ -4575,11 +4575,11 @@
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>24340</v>
+        <v>0</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>+24340</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4590,11 +4590,11 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>26258</v>
+        <v>0</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>+25358</t>
+          <t>-900</t>
         </is>
       </c>
     </row>
@@ -4605,11 +4605,11 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>25869</v>
+        <v>0</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>+25869</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4620,11 +4620,11 @@
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>26740</v>
+        <v>0</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>+26740</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4635,11 +4635,11 @@
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>66848</v>
+        <v>0</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>+29298</t>
+          <t>-37550</t>
         </is>
       </c>
     </row>
@@ -4650,11 +4650,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>85790</v>
+        <v>0</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+33279</t>
+          <t>-52511</t>
         </is>
       </c>
     </row>
@@ -4665,11 +4665,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>47198</v>
+        <v>0</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+30176</t>
+          <t>-17022</t>
         </is>
       </c>
     </row>
@@ -4680,11 +4680,11 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>45879</v>
+        <v>0</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>+28754</t>
+          <t>-17125</t>
         </is>
       </c>
     </row>
@@ -4695,11 +4695,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>45848</v>
+        <v>0</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+25712</t>
+          <t>-20136</t>
         </is>
       </c>
     </row>
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>92307</v>
+        <v>0</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+31764</t>
+          <t>-60543</t>
         </is>
       </c>
     </row>
@@ -4725,11 +4725,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>25226</v>
+        <v>0</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+24951</t>
+          <t>-275</t>
         </is>
       </c>
     </row>
@@ -4740,11 +4740,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>26815</v>
+        <v>0</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+25458</t>
+          <t>-1357</t>
         </is>
       </c>
     </row>
@@ -4755,11 +4755,11 @@
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>24293</v>
+        <v>0</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>+24293</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>58170</v>
+        <v>0</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+27997</t>
+          <t>-30173</t>
         </is>
       </c>
     </row>
@@ -4785,11 +4785,11 @@
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>20697</v>
+        <v>0</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>+20697</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4800,11 +4800,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>23673</v>
+        <v>0</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+23252</t>
+          <t>-421</t>
         </is>
       </c>
     </row>
@@ -4815,11 +4815,11 @@
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>26403</v>
+        <v>0</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>+22051</t>
+          <t>-4352</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -12,6 +12,7 @@
     <sheet name="2026-07-17" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4830,4 +4831,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-20 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>2724</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+2724</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>3834</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+3834</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>183</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+183</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3988</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+3988</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4291</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+4291</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4855</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+4855</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>4890</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+4890</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2613</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+2613</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+57</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>3582</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+3582</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Lovebird | Gorelax</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+546</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+36</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>4688</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+4688</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>780</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+780</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>3427</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+3427</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>3947</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3947</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>4063</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+4063</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -4857,7 +4857,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-20 13:01:00</t>
+          <t>Timestamp: 2026-07-20 13:31:00</t>
         </is>
       </c>
     </row>
@@ -5065,11 +5065,11 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>3834</v>
+        <v>3894</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>+3834</t>
+          <t>+3894</t>
         </is>
       </c>
     </row>
@@ -5215,11 +5215,11 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>3988</v>
+        <v>4048</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>+3988</t>
+          <t>+4048</t>
         </is>
       </c>
     </row>
@@ -5275,11 +5275,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>4291</v>
+        <v>4451</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+4291</t>
+          <t>+4451</t>
         </is>
       </c>
     </row>
@@ -5290,11 +5290,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>4855</v>
+        <v>4915</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+4855</t>
+          <t>+4915</t>
         </is>
       </c>
     </row>
@@ -5440,11 +5440,11 @@
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>3582</v>
+        <v>3642</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>+3582</t>
+          <t>+3642</t>
         </is>
       </c>
     </row>
@@ -5530,11 +5530,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>4688</v>
+        <v>4748</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+4688</t>
+          <t>+4748</t>
         </is>
       </c>
     </row>
@@ -5620,11 +5620,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1500</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -13,6 +13,7 @@
     <sheet name="2026-07-18" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5710,4 +5711,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-21 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3864</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>5286</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+1392</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>747</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+564</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5359</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+1311</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>6413</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1962</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>7441</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2526</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>6990</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2100</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2623</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>5607</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1965</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>6335</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+1587</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>780</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>4702</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1275</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>5677</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1730</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>4609</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+546</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -5737,7 +5737,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-21 13:01:00</t>
+          <t>Timestamp: 2026-07-21 13:31:00</t>
         </is>
       </c>
     </row>
@@ -6155,11 +6155,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>6413</v>
+        <v>6470</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1962</t>
+          <t>+2019</t>
         </is>
       </c>
     </row>
@@ -6170,11 +6170,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>7441</v>
+        <v>7561</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2526</t>
+          <t>+2646</t>
         </is>
       </c>
     </row>
@@ -6215,11 +6215,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>6990</v>
+        <v>7110</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+2100</t>
+          <t>+2220</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -14,6 +14,7 @@
     <sheet name="2026-07-19" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6590,4 +6591,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-22 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>3864</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>6501</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+1215</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2067</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6547</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+1188</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1140</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1140</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>8162</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1692</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>10120</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2559</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>9894</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2784</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+855</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2623</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>6792</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1185</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>6335</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>780</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>6517</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1815</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>8312</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2635</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>4837</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+228</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -15,6 +15,7 @@
     <sheet name="2026-07-20" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7470,4 +7471,883 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-23 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4137</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+273</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>6571</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+70</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3453</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1386</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>6547</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1905</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+765</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>9917</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1695</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>13042</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2802</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>12324</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2430</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2623</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>6792</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>546</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>6335</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>7957</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>11059</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2687</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>750</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>6142</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1305</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+351</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -7497,7 +7497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-23 13:01:00</t>
+          <t>Timestamp: 2026-07-23 13:31:00</t>
         </is>
       </c>
     </row>
@@ -7915,11 +7915,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>9917</v>
+        <v>10097</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1695</t>
+          <t>+1875</t>
         </is>
       </c>
     </row>
@@ -7930,11 +7930,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>13042</v>
+        <v>13102</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2802</t>
+          <t>+2862</t>
         </is>
       </c>
     </row>
@@ -8230,11 +8230,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>11059</v>
+        <v>11119</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2687</t>
+          <t>+2747</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -16,6 +16,7 @@
     <sheet name="2026-07-21" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1320,6 +1321,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-24 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4137</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+1341</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4539</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1086</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+735</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2565</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+660</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>11645</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1548</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>15769</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2667</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>14764</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2440</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2623</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+1332</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>846</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>6797</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+462</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>10459</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2502</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>13289</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2170</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1180</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+430</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1590</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+90</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+191</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>7042</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+900</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -1345,7 +1345,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-24 13:01:00</t>
+          <t>Timestamp: 2026-07-24 13:31:00</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>11645</v>
+        <v>11693</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1548</t>
+          <t>+1596</t>
         </is>
       </c>
     </row>
@@ -1778,11 +1778,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>15769</v>
+        <v>15829</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2667</t>
+          <t>+2727</t>
         </is>
       </c>
     </row>
@@ -1823,11 +1823,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>14764</v>
+        <v>14884</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+2440</t>
+          <t>+2560</t>
         </is>
       </c>
     </row>
@@ -2018,11 +2018,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>6797</v>
+        <v>6857</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+462</t>
+          <t>+522</t>
         </is>
       </c>
     </row>
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>10459</v>
+        <v>10639</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+2502</t>
+          <t>+2682</t>
         </is>
       </c>
     </row>
@@ -2078,11 +2078,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>13289</v>
+        <v>13349</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2170</t>
+          <t>+2230</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -17,6 +17,7 @@
     <sheet name="2026-07-22" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2200,6 +2201,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-25 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>X y l o t a [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4137</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>5944</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1405</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3609</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+1044</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>14213</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+2520</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>18229</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2400</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>17344</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2460</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2623</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1446</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>9506</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2649</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>11750</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>16160</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2811</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1590</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>8695</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1653</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -2225,7 +2225,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-25 13:01:00</t>
+          <t>Timestamp: 2026-07-25 13:31:00</t>
         </is>
       </c>
     </row>
@@ -2643,11 +2643,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>14213</v>
+        <v>14333</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+2520</t>
+          <t>+2640</t>
         </is>
       </c>
     </row>
@@ -2658,11 +2658,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>18229</v>
+        <v>18349</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2400</t>
+          <t>+2520</t>
         </is>
       </c>
     </row>
@@ -2703,11 +2703,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>17344</v>
+        <v>17584</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+2460</t>
+          <t>+2700</t>
         </is>
       </c>
     </row>
@@ -2898,11 +2898,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>9506</v>
+        <v>9626</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+2649</t>
+          <t>+2769</t>
         </is>
       </c>
     </row>
@@ -3018,11 +3018,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>8695</v>
+        <v>8815</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+1653</t>
+          <t>+1773</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -18,6 +18,7 @@
     <sheet name="2026-07-23" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="2026-07-26" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3080,6 +3081,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-26 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota X Neverlose</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4257</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>5944</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4844</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1544</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3609</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>19202</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+4869</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>23365</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+5016</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>22877</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+5293</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2623</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2646</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15003</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+5377</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>14502</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2752</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>20884</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+4724</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1590</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>11095</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2280</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -3105,7 +3105,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-26 13:01:00</t>
+          <t>Timestamp: 2026-07-26 13:31:00</t>
         </is>
       </c>
     </row>
@@ -3523,11 +3523,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>19202</v>
+        <v>19442</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+4869</t>
+          <t>+5109</t>
         </is>
       </c>
     </row>
@@ -3538,11 +3538,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>23365</v>
+        <v>23725</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+5016</t>
+          <t>+5376</t>
         </is>
       </c>
     </row>
@@ -3583,11 +3583,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>22877</v>
+        <v>23237</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+5293</t>
+          <t>+5653</t>
         </is>
       </c>
     </row>
@@ -3778,11 +3778,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>15003</v>
+        <v>15243</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+5377</t>
+          <t>+5617</t>
         </is>
       </c>
     </row>
@@ -3898,11 +3898,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>11095</v>
+        <v>11223</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2280</t>
+          <t>+2408</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -19,6 +19,7 @@
     <sheet name="2026-07-24" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="2026-07-26" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="2026-07-27" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3960,6 +3961,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-27 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+48</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota X Neverlose</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>4539</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+282</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>5944</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5684</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3609</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>23570</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+4128</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>31157</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+7432</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>28221</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+4984</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2646</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>17646</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+3144</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>26967</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+6083</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1590</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>13429</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2206</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -3985,7 +3985,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-27 13:01:00</t>
+          <t>Timestamp: 2026-07-27 13:31:00</t>
         </is>
       </c>
     </row>
@@ -4703,11 +4703,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>17646</v>
+        <v>17814</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+3144</t>
+          <t>+3312</t>
         </is>
       </c>
     </row>
@@ -4718,11 +4718,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>26967</v>
+        <v>27051</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+6083</t>
+          <t>+6167</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -20,6 +20,7 @@
     <sheet name="2026-07-25" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="2026-07-26" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="2026-07-27" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="2026-07-28" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4840,6 +4841,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-28 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota X Neverlose</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5379</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>7624</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1680</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5684</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3609</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>24578</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>35318</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+4161</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>29733</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1512</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Yamato Senju</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3066</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>19481</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1667</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>30856</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3805</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1590</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>14185</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+756</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>3333</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3313</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -4865,7 +4865,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-28 13:01:00</t>
+          <t>Timestamp: 2026-07-28 13:31:00</t>
         </is>
       </c>
     </row>
@@ -5283,11 +5283,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>24578</v>
+        <v>24662</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1008</t>
+          <t>+1092</t>
         </is>
       </c>
     </row>
@@ -5298,11 +5298,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>35318</v>
+        <v>35402</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+4161</t>
+          <t>+4245</t>
         </is>
       </c>
     </row>
@@ -5598,11 +5598,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>30856</v>
+        <v>30940</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3805</t>
+          <t>+3889</t>
         </is>
       </c>
     </row>
@@ -5688,11 +5688,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>3333</v>
+        <v>3417</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+3313</t>
+          <t>+3397</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -21,6 +21,7 @@
     <sheet name="2026-07-26" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="2026-07-27" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="2026-07-28" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="2026-07-29" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5720,6 +5721,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-29 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota X Neverlose</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5379</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>8848</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1224</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6068</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+384</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4449</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>26978</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+2316</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>38891</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3489</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>32643</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2910</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Yamato Senju</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3066</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>20727</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1246</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>34490</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3550</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>14857</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+672</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6671</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3254</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -5745,7 +5745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-29 13:01:00</t>
+          <t>Timestamp: 2026-07-29 13:31:00</t>
         </is>
       </c>
     </row>
@@ -6028,11 +6028,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>8848</v>
+        <v>8968</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+1224</t>
+          <t>+1344</t>
         </is>
       </c>
     </row>
@@ -6223,11 +6223,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>32643</v>
+        <v>32763</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+2910</t>
+          <t>+3030</t>
         </is>
       </c>
     </row>
@@ -6478,11 +6478,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>34490</v>
+        <v>34550</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3550</t>
+          <t>+3610</t>
         </is>
       </c>
     </row>
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>6671</v>
+        <v>6851</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+3254</t>
+          <t>+3434</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -22,6 +22,7 @@
     <sheet name="2026-07-27" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="2026-07-28" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="2026-07-29" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="2026-07-30" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6600,6 +6601,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-30 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota X Neverlose</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5379</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10390</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1422</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6368</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4749</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>29078</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+2100</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>41486</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2595</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>35343</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2580</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1545</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3366</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+960</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>21027</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>37370</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>15217</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>9110</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+2259</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>951</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -6625,7 +6625,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-30 13:01:00</t>
+          <t>Timestamp: 2026-07-30 13:31:00</t>
         </is>
       </c>
     </row>
@@ -7058,11 +7058,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>41486</v>
+        <v>41546</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2595</t>
+          <t>+2655</t>
         </is>
       </c>
     </row>
@@ -7358,11 +7358,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>37370</v>
+        <v>37430</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2880</t>
         </is>
       </c>
     </row>
@@ -7448,11 +7448,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>9110</v>
+        <v>9170</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+2259</t>
+          <t>+2319</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -23,6 +23,7 @@
     <sheet name="2026-07-28" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="2026-07-29" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="2026-07-30" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="2026-07-31" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7480,6 +7481,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-07-31 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota X Neverlose</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5670</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+291</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+250</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11660</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1270</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6668</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5049</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>30908</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1830</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>44294</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2748</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>37122</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1779</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1545</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3366</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>21037</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>40070</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2640</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>15733</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+516</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>11669</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+2499</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1262</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+311</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -7505,7 +7505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-07-31 13:01:00</t>
+          <t>Timestamp: 2026-07-31 13:31:00</t>
         </is>
       </c>
     </row>
@@ -7923,11 +7923,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>30908</v>
+        <v>30968</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1830</t>
+          <t>+1890</t>
         </is>
       </c>
     </row>
@@ -7938,11 +7938,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>44294</v>
+        <v>44354</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2748</t>
+          <t>+2808</t>
         </is>
       </c>
     </row>
@@ -7983,11 +7983,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>37122</v>
+        <v>37182</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+1779</t>
+          <t>+1839</t>
         </is>
       </c>
     </row>
@@ -8238,11 +8238,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>40070</v>
+        <v>40130</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2640</t>
+          <t>+2700</t>
         </is>
       </c>
     </row>
@@ -8328,11 +8328,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>11669</v>
+        <v>11729</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+2499</t>
+          <t>+2559</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -24,6 +24,7 @@
     <sheet name="2026-07-29" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="2026-07-30" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="2026-07-31" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="2026-08-01" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8360,6 +8361,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-01 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota X Neverlose</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>5970</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11960</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6968</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5049</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>32948</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1980</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>45854</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39162</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1980</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1545</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3666</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>21799</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+762</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>41993</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1863</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>16784</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>13619</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1890</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1262</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -8385,7 +8385,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-01 13:01:00</t>
+          <t>Timestamp: 2026-08-01 13:31:00</t>
         </is>
       </c>
     </row>
@@ -9148,11 +9148,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>1890</v>
+        <v>1910</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+20</t>
         </is>
       </c>
     </row>
@@ -9178,11 +9178,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>16784</v>
+        <v>17184</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+1051</t>
+          <t>+1451</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -25,6 +25,7 @@
     <sheet name="2026-07-30" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="2026-07-31" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="2026-08-01" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="2026-08-02" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9240,6 +9241,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-02 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+120</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>6570</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>1793</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+1793</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11960</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>7568</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5049</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>32948</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>45874</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>1376</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+1376</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39762</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>3584</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+2039</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3666</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Snoopy | Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>23163</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1364</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>45602</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3609</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>21303</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+4119</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>13619</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -9265,7 +9265,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-02 13:01:00</t>
+          <t>Timestamp: 2026-08-02 13:31:00</t>
         </is>
       </c>
     </row>
@@ -9998,11 +9998,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>45602</v>
+        <v>45722</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3609</t>
+          <t>+3729</t>
         </is>
       </c>
     </row>
@@ -10058,11 +10058,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>21303</v>
+        <v>21429</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+4119</t>
+          <t>+4245</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -26,6 +26,7 @@
     <sheet name="2026-07-31" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="2026-08-01" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="2026-08-02" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="2026-08-03" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10999,6 +11000,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-03 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>582</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>7290</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5399</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+3606</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11960</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>8168</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5049</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>32948</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>46714</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>4123</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+2747</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39762</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>7304</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+3720</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3666</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24344</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>50729</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+5007</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1910</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>25103</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3674</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>13619</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -11024,7 +11024,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-03 13:01:00</t>
+          <t>Timestamp: 2026-08-03 13:31:00</t>
         </is>
       </c>
     </row>
@@ -11292,11 +11292,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>5399</v>
+        <v>5459</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+3606</t>
+          <t>+3666</t>
         </is>
       </c>
     </row>
@@ -11547,11 +11547,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>7304</v>
+        <v>7364</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+3720</t>
+          <t>+3780</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -27,6 +27,7 @@
     <sheet name="2026-08-01" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="2026-08-02" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="2026-08-03" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="2026-08-04" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -11879,6 +11880,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-04 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>592</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>7650</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>611</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+611</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>6479</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11960</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>8468</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5589</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>32948</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>46714</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>5403</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+1280</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39762</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>8384</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3666</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24344</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>53004</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2275</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2040</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+130</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>27653</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2550</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>13619</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -11904,7 +11904,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-04 13:01:00</t>
+          <t>Timestamp: 2026-08-04 13:31:00</t>
         </is>
       </c>
     </row>
@@ -12637,11 +12637,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>53004</v>
+        <v>53064</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2275</t>
+          <t>+2335</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -28,6 +28,7 @@
     <sheet name="2026-08-02" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="2026-08-03" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="2026-08-04" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="2026-08-05" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -12759,6 +12760,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-05 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>I Am Dead  @_@</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>592</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8010</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>621</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>7970</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+1491</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11960</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+50</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>8768</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5589</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>32948</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>47074</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>6876</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+1473</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39762</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>9897</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1513</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3666</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15243</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24344</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>55884</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>29468</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1815</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>14819</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -12784,7 +12784,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-05 13:01:00</t>
+          <t>Timestamp: 2026-08-05 13:31:00</t>
         </is>
       </c>
     </row>
@@ -13517,11 +13517,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>55884</v>
+        <v>55944</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2880</t>
         </is>
       </c>
     </row>
@@ -13607,11 +13607,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>14819</v>
+        <v>15079</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+1200</t>
+          <t>+1460</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -29,6 +29,7 @@
     <sheet name="2026-08-03" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="2026-08-04" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="2026-08-05" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="2026-08-06" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13639,6 +13640,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-06 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>300K Tokens LetsGo!</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>592</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8310</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>621</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>9422</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+1452</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11960</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>9068</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5589</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>32948</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>47746</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+672</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>8613</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+1737</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39762</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>350K All in</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>11534</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3666</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>16851</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+1608</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24354</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>59004</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3060</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>32444</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2976</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>18091</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -13664,7 +13664,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-06 13:01:00</t>
+          <t>Timestamp: 2026-08-06 13:31:00</t>
         </is>
       </c>
     </row>
@@ -14097,11 +14097,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>47746</v>
+        <v>47806</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+672</t>
+          <t>+732</t>
         </is>
       </c>
     </row>
@@ -14337,11 +14337,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>16851</v>
+        <v>16911</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+1608</t>
+          <t>+1668</t>
         </is>
       </c>
     </row>
@@ -14397,11 +14397,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>59004</v>
+        <v>59054</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3060</t>
+          <t>+3110</t>
         </is>
       </c>
     </row>
@@ -14457,11 +14457,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>32444</v>
+        <v>32504</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2976</t>
+          <t>+3036</t>
         </is>
       </c>
     </row>
@@ -14487,11 +14487,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>18091</v>
+        <v>18151</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+3012</t>
+          <t>+3072</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -30,6 +30,7 @@
     <sheet name="2026-08-04" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="2026-08-05" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="2026-08-06" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="2026-08-07" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14519,6 +14520,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-07 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>300K Tokens LetsGo!</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>592</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>8310</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>621</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>9422</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11960</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>9908</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5589</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>32948</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>48366</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+560</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>8613</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39762</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>350K All in</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>11534</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3666</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>20222</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+3311</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24354</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>62816</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3762</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2060</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>35201</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2697</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>21836</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3685</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -14544,7 +14544,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-07 13:01:00</t>
+          <t>Timestamp: 2026-08-07 13:31:00</t>
         </is>
       </c>
     </row>
@@ -15217,11 +15217,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>20222</v>
+        <v>20282</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+3311</t>
+          <t>+3371</t>
         </is>
       </c>
     </row>
@@ -15277,11 +15277,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>62816</v>
+        <v>62876</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3762</t>
+          <t>+3822</t>
         </is>
       </c>
     </row>
@@ -15307,11 +15307,11 @@
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+10</t>
         </is>
       </c>
     </row>
@@ -15337,11 +15337,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>35201</v>
+        <v>35261</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2697</t>
+          <t>+2757</t>
         </is>
       </c>
     </row>
@@ -15367,11 +15367,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>21836</v>
+        <v>21896</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+3685</t>
+          <t>+3745</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -31,6 +31,7 @@
     <sheet name="2026-08-05" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="2026-08-06" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="2026-08-07" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="2026-08-08" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -15399,6 +15400,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-08 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>961</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+961</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>300K Tokens LetsGo!</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1389</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+797</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9326</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+1016</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>621</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Tuyu|Fortuners</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>7912</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>9422</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11960</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7282</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>10581</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+673</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>5589</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>32948</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>48823</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>8613</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>39762</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>350K All in</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>11534</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2651</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>778</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+778</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>8124</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>3666</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>23025</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2743</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>766</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+466</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>25962</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1608</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>65906</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3030</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1430</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>2070</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>37509</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2248</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>24752</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+2856</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -15424,7 +15424,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-08 13:01:00</t>
+          <t>Timestamp: 2026-08-08 13:31:00</t>
         </is>
       </c>
     </row>
@@ -16097,11 +16097,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>23025</v>
+        <v>23145</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+2743</t>
+          <t>+2863</t>
         </is>
       </c>
     </row>
@@ -16157,11 +16157,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>65906</v>
+        <v>66026</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3030</t>
+          <t>+3150</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -32,6 +32,7 @@
     <sheet name="2026-08-06" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="2026-08-07" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="2026-08-08" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="2026-08-09" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16279,6 +16280,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-09 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>29770</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+28809</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>300K Tokens LetsGo!</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>25009</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+24989</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>26049</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+25209</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>21021</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+19632</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>23879</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+23873</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>29023</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+29023</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>19050</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>16131</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+16131</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>39805</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+30479</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>15428</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+15108</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>18006</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+17385</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>29311</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+29311</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>21573</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+21322</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>25802</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+25802</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>28796</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+28796</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>28908</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+28874</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>37257</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+27835</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>36707</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+24747</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14558</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+14558</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>27667</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+27667</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>27423</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+27003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>28409</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+28359</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>35328</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+28046</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>39401</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+28820</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>27598</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+22009</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>28725</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+28725</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>59848</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+26900</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>74851</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+26028</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>29535</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+29535</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>23520</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+14907</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>56954</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+17192</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>23635</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+23635</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>23619</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+23619</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>33785</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>22402</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+19751</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>29661</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+28883</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>28816</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+28759</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>23421</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+15297</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>26957</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+26957</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>30793</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+27127</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>27113</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+27113</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>28524</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+28524</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>28683</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+28647</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>55017</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+31872</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>30999</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+28599</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>29493</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+28727</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>47422</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+21460</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>96586</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+30560</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>29715</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+28285</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>30822</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+28752</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>23204</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+21573</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>56793</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+19284</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>19547</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+18647</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>54191</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+29439</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>27604</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+25742</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -16304,7 +16304,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-09 13:01:00</t>
+          <t>Timestamp: 2026-08-09 13:31:00</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -33,6 +33,7 @@
     <sheet name="2026-08-07" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="2026-08-08" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="2026-08-09" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="2026-08-10" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17159,6 +17160,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-10 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>-29770</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>330</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>-25719</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>-21021</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>-23879</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-29023</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>-19050</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>-16131</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>342</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>-39463</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>-15428</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>-18006</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>-29311</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>-21573</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>-25802</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>-28796</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>-28908</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>-37257</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>-36707</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>-14558</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>-27667</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>786</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>-26637</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>-28409</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>-35328</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>-39401</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>-27598</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>-28725</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>-59848</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-74851</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>-29535</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>-23520</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>683</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>-56271</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>-23635</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>-23619</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>-33785</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>-22392</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>-29661</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>-28816</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>-23421</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>-26957</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>-30793</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>-27113</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>-28524</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>-28683</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>-55017</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>-30999</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>-29493</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>783</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>-46639</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>626</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>-95960</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>-29715</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>-30822</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>-23204</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>1257</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>-55536</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>-19547</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>1205</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>-52986</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>-27004</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -17184,7 +17184,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-10 13:01:00</t>
+          <t>Timestamp: 2026-08-10 13:31:00</t>
         </is>
       </c>
     </row>
@@ -17332,11 +17332,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>342</v>
+        <v>1092</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>-39463</t>
+          <t>-38713</t>
         </is>
       </c>
     </row>
@@ -17512,11 +17512,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>786</v>
+        <v>936</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>-26637</t>
+          <t>-26487</t>
         </is>
       </c>
     </row>
@@ -17917,11 +17917,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>626</v>
+        <v>926</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>-95960</t>
+          <t>-95660</t>
         </is>
       </c>
     </row>
@@ -18007,11 +18007,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>1205</v>
+        <v>1355</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>-52986</t>
+          <t>-52836</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -34,6 +34,7 @@
     <sheet name="2026-08-08" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="2026-08-09" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="2026-08-10" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="2026-08-11" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18039,6 +18040,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-11 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1393</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+1063</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>3146</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+2054</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+150</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>3055</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+2119</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>683</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>2306</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1523</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>5335</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+4409</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+19</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2951</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1694</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>5517</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+4162</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -18064,7 +18064,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-11 13:01:00</t>
+          <t>Timestamp: 2026-08-11 13:31:00</t>
         </is>
       </c>
     </row>
@@ -18782,11 +18782,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>2306</v>
+        <v>2391</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+1523</t>
+          <t>+1608</t>
         </is>
       </c>
     </row>
@@ -18797,11 +18797,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>5335</v>
+        <v>5419</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+4409</t>
+          <t>+4493</t>
         </is>
       </c>
     </row>
@@ -18902,11 +18902,11 @@
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>600</v>
+        <v>698</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+98</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -35,6 +35,7 @@
     <sheet name="2026-08-09" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="2026-08-10" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="2026-08-11" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="2026-08-12" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18919,6 +18920,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-12 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1393</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1508</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1508</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4126</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+980</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+108</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+3900</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>683</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>4899</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+3819</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morri§ey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>4474</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2083</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>10430</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+5011</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2951</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>5517</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1238</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -18944,7 +18944,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-12 13:01:00</t>
+          <t>Timestamp: 2026-08-12 13:31:00</t>
         </is>
       </c>
     </row>
@@ -19617,11 +19617,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>4899</v>
+        <v>5007</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+3819</t>
+          <t>+3927</t>
         </is>
       </c>
     </row>
@@ -19677,11 +19677,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>10430</v>
+        <v>10538</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+5011</t>
+          <t>+5119</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -36,6 +36,7 @@
     <sheet name="2026-08-10" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="2026-08-11" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="2026-08-12" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="2026-08-13" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20678,6 +20679,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-13 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+563</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3452</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1944</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>6394</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+2268</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Khakashi Hatake</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>683</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>10032</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+5025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Ary</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>4986</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>14352</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3814</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2951</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6039</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+522</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1238</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -20703,7 +20703,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-13 13:01:00</t>
+          <t>Timestamp: 2026-08-13 13:31:00</t>
         </is>
       </c>
     </row>
@@ -20806,11 +20806,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>3452</v>
+        <v>3560</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+1944</t>
+          <t>+2052</t>
         </is>
       </c>
     </row>
@@ -21376,11 +21376,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>10032</v>
+        <v>10140</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+5025</t>
+          <t>+5133</t>
         </is>
       </c>
     </row>
@@ -21436,11 +21436,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>14352</v>
+        <v>14478</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3814</t>
+          <t>+3940</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -37,6 +37,7 @@
     <sheet name="2026-08-11" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="2026-08-12" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="2026-08-13" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="2026-08-14" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21558,6 +21559,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-14 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+972</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+2456</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Kosaki</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Meru™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>683</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>12357</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2217</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>6805</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1819</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>19297</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+4819</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>595</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+576</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2951</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6039</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1778</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -21583,7 +21583,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-14 13:01:00</t>
+          <t>Timestamp: 2026-08-14 13:31:00</t>
         </is>
       </c>
     </row>
@@ -22256,11 +22256,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>12357</v>
+        <v>12465</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+2217</t>
+          <t>+2325</t>
         </is>
       </c>
     </row>
@@ -22301,11 +22301,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>6805</v>
+        <v>7021</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+1819</t>
+          <t>+2035</t>
         </is>
       </c>
     </row>
@@ -22316,11 +22316,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>19297</v>
+        <v>19405</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+4819</t>
+          <t>+4927</t>
         </is>
       </c>
     </row>
@@ -22376,11 +22376,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>2951</v>
+        <v>3491</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+540</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -38,6 +38,7 @@
     <sheet name="2026-08-12" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="2026-08-13" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="2026-08-14" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="2026-08-15" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22438,6 +22439,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-15 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Prince G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1296</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2087</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1404</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>15757</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+3292</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>10225</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+3204</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>24396</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+4991</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>595</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>8306</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+4815</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6039</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1868</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+90</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -22463,7 +22463,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-15 13:01:00</t>
+          <t>Timestamp: 2026-08-15 13:31:00</t>
         </is>
       </c>
     </row>
@@ -22881,11 +22881,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>1296</v>
+        <v>2376</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1296</t>
+          <t>+2376</t>
         </is>
       </c>
     </row>
@@ -22941,11 +22941,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>2087</v>
+        <v>3167</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+1404</t>
+          <t>+2484</t>
         </is>
       </c>
     </row>
@@ -23181,11 +23181,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>10225</v>
+        <v>10585</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+3204</t>
+          <t>+3564</t>
         </is>
       </c>
     </row>
@@ -23196,11 +23196,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>24396</v>
+        <v>24612</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+4991</t>
+          <t>+5207</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -39,6 +39,7 @@
     <sheet name="2026-08-13" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="2026-08-14" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="2026-08-15" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="2026-08-16" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23318,6 +23319,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-16 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>324</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+288</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>5692</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+3316</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>11235</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+8068</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>24304</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+8547</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>15845</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+5260</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>34554</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+9942</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+74</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>2160</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+2160</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>18073</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+9767</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6039</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1868</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -23343,7 +23343,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-16 13:01:00</t>
+          <t>Timestamp: 2026-08-16 13:31:00</t>
         </is>
       </c>
     </row>
@@ -24076,11 +24076,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>34554</v>
+        <v>34770</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+9942</t>
+          <t>+10158</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -40,6 +40,7 @@
     <sheet name="2026-08-14" sheetId="31" state="visible" r:id="rId31"/>
     <sheet name="2026-08-15" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="2026-08-16" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="2026-08-17" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24198,6 +24199,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-17 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>504</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+180</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>7852</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+2160</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>18188</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+6953</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>29488</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+5184</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>20309</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+4464</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>44747</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+9977</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>3205</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>24985</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+6912</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6039</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1868</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -24223,7 +24223,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-17 13:01:00</t>
+          <t>Timestamp: 2026-08-17 13:31:00</t>
         </is>
       </c>
     </row>
@@ -24941,11 +24941,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>20309</v>
+        <v>20849</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+4464</t>
+          <t>+5004</t>
         </is>
       </c>
     </row>
@@ -24956,11 +24956,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>44747</v>
+        <v>44855</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+9977</t>
+          <t>+10085</t>
         </is>
       </c>
     </row>
@@ -25061,11 +25061,11 @@
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>1868</v>
+        <v>1940</v>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+72</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -41,6 +41,7 @@
     <sheet name="2026-08-15" sheetId="32" state="visible" r:id="rId32"/>
     <sheet name="2026-08-16" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="2026-08-17" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="2026-08-18" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25078,6 +25079,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-18 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>612</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+108</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>7852</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>18188</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>32358</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2870</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>23801</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+2952</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>49914</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+5059</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>669</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5223</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+2018</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>26793</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1808</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6039</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1940</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -25103,7 +25103,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-18 13:01:00</t>
+          <t>Timestamp: 2026-08-18 13:31:00</t>
         </is>
       </c>
     </row>
@@ -25836,11 +25836,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>49914</v>
+        <v>50022</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+5059</t>
+          <t>+5167</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -42,6 +42,7 @@
     <sheet name="2026-08-16" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="2026-08-17" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="2026-08-18" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="2026-08-19" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25958,6 +25959,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-19 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>.</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>612</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>7852</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>18188</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>36013</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+3655</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>24899</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>55098</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+5076</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+108</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5241</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>31869</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+5076</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6039</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -25983,7 +25983,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-19 13:01:00</t>
+          <t>Timestamp: 2026-08-19 13:31:00</t>
         </is>
       </c>
     </row>
@@ -26701,11 +26701,11 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>24899</v>
+        <v>25169</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>+1098</t>
+          <t>+1368</t>
         </is>
       </c>
     </row>
@@ -26716,11 +26716,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>55098</v>
+        <v>55206</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+5076</t>
+          <t>+5184</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -43,6 +43,7 @@
     <sheet name="2026-08-17" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="2026-08-18" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="2026-08-19" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="2026-08-20" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26838,6 +26839,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-20 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Spirit</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>630</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>4532</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>6955</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>7852</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>540</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>18188</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>38463</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2450</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>25169</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>59874</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+4668</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5241</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>35655</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3786</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>6039</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -26863,7 +26863,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-20 13:01:00</t>
+          <t>Timestamp: 2026-08-20 13:31:00</t>
         </is>
       </c>
     </row>
@@ -27596,11 +27596,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>59874</v>
+        <v>59982</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+4668</t>
+          <t>+4776</t>
         </is>
       </c>
     </row>
@@ -27656,11 +27656,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>35655</v>
+        <v>35763</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+3786</t>
+          <t>+3894</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -44,6 +44,7 @@
     <sheet name="2026-08-18" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="2026-08-19" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="2026-08-20" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="2026-08-21" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27718,6 +27719,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-21 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>630</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>6800</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+2268</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>DangerousEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Xylota x [NvL]</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>540</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>BlackObito™</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>9871</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+2916</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Izx Infernity</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>9256</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1404</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>BlacKoreana O</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>4320</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3780</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>19484</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1296</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>40839</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+2376</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Morrissey †</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>25710</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>64956</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+4974</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5241</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>40646</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+4883</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>9063</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>2516</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+36</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -27743,7 +27743,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-21 13:01:00</t>
+          <t>Timestamp: 2026-08-21 13:31:00</t>
         </is>
       </c>
     </row>
@@ -27846,11 +27846,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>6800</v>
+        <v>6908</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+2268</t>
+          <t>+2376</t>
         </is>
       </c>
     </row>
@@ -28071,11 +28071,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>9871</v>
+        <v>9979</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>+2916</t>
+          <t>+3024</t>
         </is>
       </c>
     </row>
@@ -28161,11 +28161,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>9256</v>
+        <v>9364</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1404</t>
+          <t>+1512</t>
         </is>
       </c>
     </row>
@@ -28176,11 +28176,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>4320</v>
+        <v>4536</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+3780</t>
+          <t>+3996</t>
         </is>
       </c>
     </row>
@@ -28221,11 +28221,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>19484</v>
+        <v>19598</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+1296</t>
+          <t>+1410</t>
         </is>
       </c>
     </row>
@@ -28476,11 +28476,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>64956</v>
+        <v>65064</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+4974</t>
+          <t>+5082</t>
         </is>
       </c>
     </row>
@@ -28566,11 +28566,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>9063</v>
+        <v>9171</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+3024</t>
+          <t>+3132</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -45,6 +45,7 @@
     <sheet name="2026-08-19" sheetId="36" state="visible" r:id="rId36"/>
     <sheet name="2026-08-20" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="2026-08-21" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="2026-08-22" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28598,6 +28599,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-22 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>666</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>10688</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+3780</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ReinEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>540</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>13759</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+3780</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+523</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>12496</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+3132</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>8066</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>LA NEGRA MATEA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>22406</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>540</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>44943</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+4104</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sirius Kurogaeshi</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>25746</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>70140</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+5076</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5241</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>44231</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3585</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>13457</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+4286</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>2516</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -28623,7 +28623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-22 13:01:00</t>
+          <t>Timestamp: 2026-08-22 13:31:00</t>
         </is>
       </c>
     </row>
@@ -28726,11 +28726,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>10688</v>
+        <v>10904</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+3780</t>
+          <t>+3996</t>
         </is>
       </c>
     </row>
@@ -29041,11 +29041,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>12496</v>
+        <v>12712</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+3132</t>
+          <t>+3348</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>8066</v>
+        <v>9146</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>22406</v>
+        <v>22622</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Sirius Kurogaeshi</t>
+          <t>Sirius Impera</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -29356,11 +29356,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>70140</v>
+        <v>70356</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+5076</t>
+          <t>+5292</t>
         </is>
       </c>
     </row>
@@ -29446,11 +29446,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>13457</v>
+        <v>13568</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+4286</t>
+          <t>+4397</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -46,6 +46,7 @@
     <sheet name="2026-08-20" sheetId="37" state="visible" r:id="rId37"/>
     <sheet name="2026-08-21" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="2026-08-22" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="2026-08-23" sheetId="40" state="visible" r:id="rId40"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30357,6 +30358,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-23 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>432</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+324</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>874</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+208</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>SuhaibEX</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>14264</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+3360</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ReinEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>8850</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>540</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>13759</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>21889</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+9177</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>9851</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+705</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>LA NEGRA MATEA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>31499</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+8877</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+204</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>54045</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+9102</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2666</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+2666</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>26586</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>79344</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+8988</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5241</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>51101</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+6870</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>22337</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+8769</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>2516</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -30382,7 +30382,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-23 13:01:00</t>
+          <t>Timestamp: 2026-08-23 13:31:00</t>
         </is>
       </c>
     </row>
@@ -30485,11 +30485,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>14264</v>
+        <v>14432</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+3360</t>
+          <t>+3528</t>
         </is>
       </c>
     </row>
@@ -30800,11 +30800,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>21889</v>
+        <v>22057</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+9177</t>
+          <t>+9345</t>
         </is>
       </c>
     </row>
@@ -30860,11 +30860,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>31499</v>
+        <v>31667</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+8877</t>
+          <t>+9045</t>
         </is>
       </c>
     </row>
@@ -31055,11 +31055,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>54045</v>
+        <v>54213</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+9102</t>
+          <t>+9270</t>
         </is>
       </c>
     </row>
@@ -31070,11 +31070,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>2666</v>
+        <v>3366</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+2666</t>
+          <t>+3366</t>
         </is>
       </c>
     </row>
@@ -31100,7 +31100,7 @@
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>26586</v>
+        <v>27090</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
@@ -31115,11 +31115,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>79344</v>
+        <v>79512</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+8988</t>
+          <t>+9156</t>
         </is>
       </c>
     </row>
@@ -31175,11 +31175,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>51101</v>
+        <v>51437</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+6870</t>
+          <t>+7206</t>
         </is>
       </c>
     </row>
@@ -31205,11 +31205,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>22337</v>
+        <v>22505</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+8769</t>
+          <t>+8937</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -47,6 +47,7 @@
     <sheet name="2026-08-21" sheetId="38" state="visible" r:id="rId38"/>
     <sheet name="2026-08-22" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="2026-08-23" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="2026-08-24" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31237,6 +31238,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-24 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>432</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>902</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>18464</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+4032</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>540</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+1680</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>7107</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+7107</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>4455</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+4455</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>17185</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+3426</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>25564</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+3507</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>12879</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3028</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>6780</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+6780</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>PUCCA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>36431</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>7155</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+7155</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Flarekaze |Fortuners</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+1470</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>57411</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+3198</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>5583</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+2217</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>5073</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+5073</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1960</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>87327</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+7815</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5241</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>57296</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+5859</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>29834</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+7329</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>3302</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+786</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -31262,7 +31262,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-24 13:01:00</t>
+          <t>Timestamp: 2026-08-24 13:31:00</t>
         </is>
       </c>
     </row>
@@ -31530,11 +31530,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>7107</v>
+        <v>7191</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+7107</t>
+          <t>+7191</t>
         </is>
       </c>
     </row>
@@ -31545,11 +31545,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>4455</v>
+        <v>4539</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+4455</t>
+          <t>+4539</t>
         </is>
       </c>
     </row>
@@ -31725,11 +31725,11 @@
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>6780</v>
+        <v>6864</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>+6780</t>
+          <t>+6864</t>
         </is>
       </c>
     </row>
@@ -31785,11 +31785,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>7155</v>
+        <v>7174</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+7155</t>
+          <t>+7174</t>
         </is>
       </c>
     </row>
@@ -31935,11 +31935,11 @@
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>57411</v>
+        <v>57579</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+3198</t>
+          <t>+3366</t>
         </is>
       </c>
     </row>
@@ -31965,11 +31965,11 @@
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>5073</v>
+        <v>5157</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>+5073</t>
+          <t>+5157</t>
         </is>
       </c>
     </row>
@@ -31995,11 +31995,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>87327</v>
+        <v>87411</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+7815</t>
+          <t>+7899</t>
         </is>
       </c>
     </row>
@@ -32055,11 +32055,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>57296</v>
+        <v>57716</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+5859</t>
+          <t>+6279</t>
         </is>
       </c>
     </row>
@@ -32085,11 +32085,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>29834</v>
+        <v>29918</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+7329</t>
+          <t>+7413</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -48,6 +48,7 @@
     <sheet name="2026-08-22" sheetId="39" state="visible" r:id="rId39"/>
     <sheet name="2026-08-23" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="2026-08-24" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="2026-08-25" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32117,6 +32118,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-25 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>432</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>902</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>18464</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2976</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+2436</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+350</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>11022</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+3831</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>7206</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2667</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>17185</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>27160</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+1596</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>14139</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1260</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>10669</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+3805</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>PUCCA</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>37943</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+1512</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>9629</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+2455</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>DeVana</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>61053</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+3474</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>5595</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>8865</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+3708</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>91281</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3870</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5241</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>61023</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3307</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>32858</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+2940</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>3722</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -32142,7 +32142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-25 13:01:00</t>
+          <t>Timestamp: 2026-08-25 13:31:00</t>
         </is>
       </c>
     </row>
@@ -32305,11 +32305,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>2976</v>
+        <v>3060</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+2436</t>
+          <t>+2520</t>
         </is>
       </c>
     </row>
@@ -32410,11 +32410,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>11022</v>
+        <v>11106</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+3831</t>
+          <t>+3915</t>
         </is>
       </c>
     </row>
@@ -32560,11 +32560,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>27160</v>
+        <v>27244</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+1596</t>
+          <t>+1680</t>
         </is>
       </c>
     </row>
@@ -32620,11 +32620,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>37943</v>
+        <v>38111</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+1512</t>
+          <t>+1680</t>
         </is>
       </c>
     </row>
@@ -32665,11 +32665,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>9629</v>
+        <v>9714</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+2455</t>
+          <t>+2540</t>
         </is>
       </c>
     </row>
@@ -32875,11 +32875,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>91281</v>
+        <v>91365</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3870</t>
+          <t>+3954</t>
         </is>
       </c>
     </row>
@@ -32965,11 +32965,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>32858</v>
+        <v>32923</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+2940</t>
+          <t>+3005</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -49,6 +49,7 @@
     <sheet name="2026-08-23" sheetId="40" state="visible" r:id="rId40"/>
     <sheet name="2026-08-24" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="2026-08-25" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="2026-08-26" sheetId="43" state="visible" r:id="rId43"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32997,6 +32998,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-26 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2618</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+2618</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>432</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2496</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>902</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>18464</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>10095</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+7035</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>14963</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+3857</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>11030</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+3824</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>17185</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>30364</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+3120</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>16646</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2507</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>14279</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+3610</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>40967</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>13245</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+3531</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>3196</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+3178</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>DeVana</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>64826</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+3773</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>5595</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>12955</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+4090</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>95222</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+3857</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>777</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Rood</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>5241</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>64551</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3528</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>36703</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3780</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>3722</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -33022,7 +33022,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-26 13:01:00</t>
+          <t>Timestamp: 2026-08-26 13:31:00</t>
         </is>
       </c>
     </row>
@@ -33185,11 +33185,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>10095</v>
+        <v>10179</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+7035</t>
+          <t>+7119</t>
         </is>
       </c>
     </row>
@@ -33290,11 +33290,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>14963</v>
+        <v>15047</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+3857</t>
+          <t>+3941</t>
         </is>
       </c>
     </row>
@@ -33305,11 +33305,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>11030</v>
+        <v>11114</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+3824</t>
+          <t>+3908</t>
         </is>
       </c>
     </row>
@@ -33331,7 +33331,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>NicolasRicko</t>
+          <t>ProfessorX ?</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
@@ -33339,18 +33339,18 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Izx Hatake Jr</t>
+          <t>NicolasRicko</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>17185</v>
+        <v>0</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
@@ -33361,11 +33361,11 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>MATHEMATRICK</t>
+          <t>Izx Hatake Jr</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0</v>
+        <v>17185</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
@@ -33376,7 +33376,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Nabila|Fortuners</t>
+          <t>MATHEMATRICK</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -33391,11 +33391,11 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>~[AnbuDream]~</t>
+          <t>Nabila|Fortuners</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1603</v>
+        <v>0</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
@@ -33406,11 +33406,11 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Ryujin Senju™</t>
+          <t>~[AnbuDream]~</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0</v>
+        <v>1603</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -33421,7 +33421,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heisenberg </t>
+          <t>Ryujin Senju™</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
@@ -33436,97 +33436,97 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Tobirama Senju™</t>
+          <t xml:space="preserve">Heisenberg </t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>30364</v>
+        <v>0</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>+3120</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>ZenithEX</t>
+          <t>Tobirama Senju™</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>16646</v>
+        <v>30364</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+2507</t>
+          <t>+3120</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>§åñÐåïmårµ | Frtners</t>
+          <t>ZenithEX</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0</v>
+        <v>16646</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+2507</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>MERU™</t>
+          <t>§åñÐåïmårµ | Frtners</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>14279</v>
+        <v>0</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>+3610</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>SNC | Vnzla Anbu |SN</t>
+          <t>MERU™</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>40967</v>
+        <v>14363</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>+3694</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>SNC | Signature</t>
+          <t>SNC | Vnzla Anbu |SN</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>0</v>
+        <v>41387</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Fusion</t>
+          <t>SNC | Signature</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
@@ -33541,41 +33541,41 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Sesshomaru</t>
+          <t>Fusion</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>13245</v>
+        <v>0</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+3531</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>KYO</t>
+          <t>Sesshomaru</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>242</v>
+        <v>13329</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3615</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nitro </t>
+          <t>KYO</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
@@ -33586,37 +33586,37 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>SL41F3RT</t>
+          <t xml:space="preserve">Nitro </t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>3196</v>
+        <v>0</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>+3178</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>DeVana</t>
+          <t>SL41F3RT</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>0</v>
+        <v>3196</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3178</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Raiden</t>
+          <t>DeVana</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
@@ -33631,11 +33631,11 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>ShadowRavenX</t>
+          <t>Raiden</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>2850</v>
+        <v>0</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
@@ -33646,11 +33646,11 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Aldrin</t>
+          <t>ShadowRavenX</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>0</v>
+        <v>2850</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>SNC | TemperiTa</t>
+          <t>Aldrin</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
@@ -33676,7 +33676,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>SmallDino</t>
+          <t>SNC | TemperiTa</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -33691,101 +33691,101 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Breaker LITE</t>
+          <t>SmallDino</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>64826</v>
+        <v>0</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>+3773</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>TYSM for Market Devs</t>
+          <t>Breaker LITE</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>5595</v>
+        <v>64994</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3941</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Arya</t>
+          <t>TYSM for Market Devs</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>12955</v>
+        <v>5595</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>+4090</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Arya</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>29050</v>
+        <v>12955</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+4090</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Jonny Brown</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>95222</v>
+        <v>29050</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>+3857</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Knightwalker</t>
+          <t>Jonny Brown</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>0</v>
+        <v>95306</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+3941</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">a fucking ninja </t>
+          <t>Knightwalker</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>777</v>
+        <v>0</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
@@ -33796,11 +33796,11 @@
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Rood</t>
+          <t xml:space="preserve">a fucking ninja </t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>5241</v>
+        <v>777</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
@@ -33845,11 +33845,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>36703</v>
+        <v>36871</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+3780</t>
+          <t>+3948</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -50,6 +50,7 @@
     <sheet name="2026-08-24" sheetId="41" state="visible" r:id="rId41"/>
     <sheet name="2026-08-25" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="2026-08-26" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="2026-08-27" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33877,6 +33878,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-27 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3556</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+938</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>895</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+463</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2916</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>902</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2604</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+2604</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>18464</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>14030</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+3851</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>18904</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+3857</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>14732</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+3618</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>2900</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+2900</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>17185</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1150</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1150</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>33633</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3269</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>19768</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+3122</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>18118</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+3755</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>44411</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+3024</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1092</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+1092</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>17186</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+3857</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>3196</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>DeVana</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1014</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>68838</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+3844</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>6015</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>17605</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+4650</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>98845</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+3539</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>910</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+910</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>791</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>68046</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3495</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>40657</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3786</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>3722</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -51,6 +51,7 @@
     <sheet name="2026-08-25" sheetId="42" state="visible" r:id="rId42"/>
     <sheet name="2026-08-26" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="2026-08-27" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="2026-08-28" sheetId="45" state="visible" r:id="rId45"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34757,6 +34758,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-28 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3556</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>895</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1344</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+924</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3216</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>902</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>6036</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+3432</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>18464</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>17542</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+3512</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>21128</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+2224</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>18236</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+3504</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3508</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+608</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>17185</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2562</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1412</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2323</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>36613</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2980</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>21472</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1704</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>20814</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2696</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>47852</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+3441</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>4558</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+3466</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>20362</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+3176</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>3196</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>DeVana</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>3209</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+2195</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>72037</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+3199</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>6927</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+912</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>19188</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1583</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>101388</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2543</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>910</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>791</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>71490</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+3444</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>44074</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3417</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4022</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -34782,7 +34782,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-28 13:01:00</t>
+          <t>Timestamp: 2026-08-28 13:31:00</t>
         </is>
       </c>
     </row>
@@ -34885,11 +34885,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>6036</v>
+        <v>6096</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+3432</t>
+          <t>+3492</t>
         </is>
       </c>
     </row>
@@ -34945,11 +34945,11 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>17542</v>
+        <v>17602</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+3512</t>
+          <t>+3572</t>
         </is>
       </c>
     </row>
@@ -35050,11 +35050,11 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>21128</v>
+        <v>21188</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+2224</t>
+          <t>+2284</t>
         </is>
       </c>
     </row>
@@ -35065,11 +35065,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>18236</v>
+        <v>18296</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+3504</t>
+          <t>+3564</t>
         </is>
       </c>
     </row>
@@ -35230,11 +35230,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>21472</v>
+        <v>21532</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>+1704</t>
+          <t>+1764</t>
         </is>
       </c>
     </row>
@@ -35260,11 +35260,11 @@
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>20814</v>
+        <v>20874</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>+2696</t>
+          <t>+2756</t>
         </is>
       </c>
     </row>
@@ -35305,11 +35305,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>4558</v>
+        <v>4618</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+3466</t>
+          <t>+3526</t>
         </is>
       </c>
     </row>
@@ -35320,11 +35320,11 @@
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>20362</v>
+        <v>20422</v>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>+3176</t>
+          <t>+3236</t>
         </is>
       </c>
     </row>
@@ -35605,11 +35605,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>44074</v>
+        <v>44134</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+3417</t>
+          <t>+3477</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -52,6 +52,7 @@
     <sheet name="2026-08-26" sheetId="43" state="visible" r:id="rId43"/>
     <sheet name="2026-08-27" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="2026-08-28" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="2026-08-29" sheetId="46" state="visible" r:id="rId46"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35637,6 +35638,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-29 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>3556</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>895</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>1344</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>3756</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>2086</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+1184</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>8916</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>18464</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1782</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1782</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>18235</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+633</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2744</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+1064</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>1047</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+1047</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>23201</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>21107</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2811</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>3528</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>17185</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3282</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+720</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2623</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>38284</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1671</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>22852</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>22974</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+2100</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>49892</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+2040</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>7420</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+2802</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>22522</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+2100</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>3196</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>FlareKaze</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>3749</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>3150</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>74804</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+2767</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>7047</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+120</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>20988</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>104282</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2894</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>910</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>791</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>74430</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2940</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>46946</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+2812</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>4022</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -35662,7 +35662,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-29 13:01:00</t>
+          <t>Timestamp: 2026-08-29 13:31:01</t>
         </is>
       </c>
     </row>
@@ -35765,11 +35765,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>8916</v>
+        <v>9036</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2940</t>
         </is>
       </c>
     </row>
@@ -35810,11 +35810,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1782</v>
+        <v>1902</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+1782</t>
+          <t>+1902</t>
         </is>
       </c>
     </row>
@@ -36050,11 +36050,11 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>2623</v>
+        <v>3223</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>+300</t>
+          <t>+900</t>
         </is>
       </c>
     </row>
@@ -36110,11 +36110,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>22852</v>
+        <v>22972</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1440</t>
         </is>
       </c>
     </row>
@@ -36155,11 +36155,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>49892</v>
+        <v>50012</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+2040</t>
+          <t>+2160</t>
         </is>
       </c>
     </row>
@@ -36185,11 +36185,11 @@
         </is>
       </c>
       <c r="B37" s="5" t="n">
-        <v>7420</v>
+        <v>7540</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>+2802</t>
+          <t>+2922</t>
         </is>
       </c>
     </row>
@@ -36410,11 +36410,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>104282</v>
+        <v>104402</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2894</t>
+          <t>+3014</t>
         </is>
       </c>
     </row>
@@ -36485,11 +36485,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>46946</v>
+        <v>47066</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+2812</t>
+          <t>+2932</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -53,6 +53,7 @@
     <sheet name="2026-08-27" sheetId="44" state="visible" r:id="rId44"/>
     <sheet name="2026-08-28" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="2026-08-29" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="2026-08-30" sheetId="47" state="visible" r:id="rId47"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36517,6 +36518,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-30 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>40062</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>+36506</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>22393</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+21498</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>23727</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>+22383</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>25921</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+22165</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>23123</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+21037</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>34467</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+25431</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>35224</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+16760</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>23753</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>+23753</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28710</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+26808</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>36279</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+18044</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>22405</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>+22147</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>33630</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+33630</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37249</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>+36899</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>20248</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>+17504</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>36879</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>+35832</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>34947</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>+34947</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>60702</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>+37501</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>44472</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+23365</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>18710</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>+18710</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>22626</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+19098</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>21216</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+21196</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>36659</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>+19474</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>17635</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>+17635</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>41258</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+37976</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>25853</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+22630</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>15581</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>+15581</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>43903</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>+43903</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>66315</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+28031</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>55737</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+32765</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>44267</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>+44267</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43363</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>+20389</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>71765</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+21753</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>21025</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>+21025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>32264</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>+24724</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>50696</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+28174</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>14208</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+13956</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>35212</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>+35212</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>21387</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>+18191</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>FlareKaze</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>29775</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+26026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>20778</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>+20778</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>25701</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+22551</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>20895</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>+20895</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>23544</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>+23544</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>22768</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>+22768</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>104537</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+29733</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>30005</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+22958</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>55514</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>+34526</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>50380</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+21330</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>129766</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+25364</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>24626</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+23716</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>24305</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+23514</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>101366</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+26936</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>24220</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>+23380</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>71119</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+24053</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>21565</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+17543</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -36542,7 +36542,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-30 13:01:00</t>
+          <t>Timestamp: 2026-08-30 13:31:00</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -54,6 +54,7 @@
     <sheet name="2026-08-28" sheetId="45" state="visible" r:id="rId45"/>
     <sheet name="2026-08-29" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="2026-08-30" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="2026-08-31" sheetId="48" state="visible" r:id="rId48"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37397,6 +37398,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-08-31 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>40062</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>22393</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>23727</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>25921</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>23123</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>34467</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>35224</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>23753</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28710</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>36279</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>22405</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>33630</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37249</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>20248</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>36879</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>34947</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>60702</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>44472</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>18710</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>22626</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>21216</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>36659</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>17635</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>41258</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>25853</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>15581</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>43903</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>66315</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>55737</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>44267</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43363</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>71765</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>21025</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>32264</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>50696</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>14208</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>35212</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>21387</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>FlareKaze</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>29775</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>20778</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>25701</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>20895</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>23544</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>22768</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>104537</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>30005</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>55514</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>50380</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>129766</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>24626</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>24305</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>101366</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>24220</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>71119</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>21565</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -37422,7 +37422,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-08-31 13:01:00</t>
+          <t>Timestamp: 2026-08-31 13:31:00</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -55,6 +55,7 @@
     <sheet name="2026-08-29" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="2026-08-30" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="2026-08-31" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="2026-09-01" sheetId="49" state="visible" r:id="rId49"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38277,6 +38278,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-01 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>40062</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>22393</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>23727</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>25921</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>23123</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>34467</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>35224</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>23753</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28710</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>36279</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>22405</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>33630</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>37249</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>20248</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>36879</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>34947</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>60702</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>44472</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>18710</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>22626</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>21216</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>36659</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>17635</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>41258</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>25853</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>15581</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>43903</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>66315</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>55737</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>44267</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>43363</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>71765</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>21025</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>32264</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>50696</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>14208</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>35212</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>21387</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>FlareKaze</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>29775</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>20778</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>25701</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>20895</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>23544</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>22768</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>104537</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>30005</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>55514</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>50380</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>129766</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>24626</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>24305</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>101366</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>24220</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>71119</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>21565</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -38302,7 +38302,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-01 13:01:00</t>
+          <t>Timestamp: 2026-09-01 13:31:00</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -56,6 +56,7 @@
     <sheet name="2026-08-30" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="2026-08-31" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="2026-09-01" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="2026-09-02" sheetId="50" state="visible" r:id="rId50"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40036,6 +40037,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-02 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>-40062</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>-22174</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>-23727</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>-25921</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>-23123</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>-34467</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>-35224</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>-23753</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>-28710</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>-36279</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>-22405</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>-33630</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>-37249</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>-20248</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>-36879</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>-34947</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>-60702</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>-44472</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>-18710</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>-22622</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>-21216</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>-36659</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>-17635</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>-41258</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>443</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>-25410</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>-15581</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>-43903</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>214</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>-66101</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>-55737</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>-44267</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>-43363</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>525</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>-71240</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>-21025</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>-32264</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>-50696</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>-14208</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>-35212</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>-21387</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Jembot Kriwil</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>-20778</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>-25701</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>-20895</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>-23544</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>-22768</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>-104537</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>-30005</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>-55514</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>-50128</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>-129766</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>-24626</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>-24305</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>-101366</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>-24220</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>-71119</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>-21565</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -40061,7 +40061,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-02 13:01:00</t>
+          <t>Timestamp: 2026-09-02 13:31:00</t>
         </is>
       </c>
     </row>
@@ -40494,11 +40494,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>-66101</t>
+          <t>-66098</t>
         </is>
       </c>
     </row>
@@ -40794,11 +40794,11 @@
         </is>
       </c>
       <c r="B51" s="5" t="n">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>-50128</t>
+          <t>-50087</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -57,6 +57,7 @@
     <sheet name="2026-08-31" sheetId="48" state="visible" r:id="rId48"/>
     <sheet name="2026-09-01" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="2026-09-02" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="2026-09-03" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40916,6 +40917,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-03 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+42</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+46</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+56</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>831</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+831</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>443</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2353</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2136</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1802</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1802</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>3001</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+2476</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+25</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>738</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2790</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+2790</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TYSM for Market Devs</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>713</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>759</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+759</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+370</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>2328</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2328</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+126</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -40941,7 +40941,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-03 13:01:00</t>
+          <t>Timestamp: 2026-09-03 13:31:00</t>
         </is>
       </c>
     </row>
@@ -41434,11 +41434,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>3001</v>
+        <v>3169</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+2476</t>
+          <t>+2644</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -58,6 +58,7 @@
     <sheet name="2026-09-01" sheetId="49" state="visible" r:id="rId49"/>
     <sheet name="2026-09-02" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="2026-09-03" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="2026-09-04" sheetId="52" state="visible" r:id="rId52"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41796,6 +41797,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-04 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>840</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>453</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+33</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+98</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>831</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>443</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5641</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3288</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1924</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>5991</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+2822</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>738</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>6354</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+3564</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>965</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+252</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>4609</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+3850</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>5222</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2894</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -41821,7 +41821,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-04 13:01:00</t>
+          <t>Timestamp: 2026-09-04 13:31:00</t>
         </is>
       </c>
     </row>
@@ -42254,11 +42254,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>5641</v>
+        <v>5809</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+3288</t>
+          <t>+3456</t>
         </is>
       </c>
     </row>
@@ -42509,11 +42509,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>6354</v>
+        <v>6438</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+3564</t>
+          <t>+3648</t>
         </is>
       </c>
     </row>
@@ -42569,11 +42569,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>4609</v>
+        <v>4693</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+3850</t>
+          <t>+3934</t>
         </is>
       </c>
     </row>
@@ -42614,11 +42614,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>5222</v>
+        <v>5306</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2894</t>
+          <t>+2978</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -59,6 +59,7 @@
     <sheet name="2026-09-02" sheetId="50" state="visible" r:id="rId50"/>
     <sheet name="2026-09-03" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="2026-09-04" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="2026-09-05" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42676,6 +42677,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-05 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>1589</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+749</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>+400</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>453</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Nabila|Fortuners</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>1671</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>443</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>9380</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+3571</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>3726</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>9892</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+3901</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+465</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>+420</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>9836</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+3398</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>2143</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+1178</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>8459</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+3766</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>8305</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2999</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -42701,7 +42701,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-05 13:01:00</t>
+          <t>Timestamp: 2026-09-05 13:31:00</t>
         </is>
       </c>
     </row>
@@ -43449,11 +43449,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>8459</v>
+        <v>8627</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+3766</t>
+          <t>+3934</t>
         </is>
       </c>
     </row>
@@ -43494,11 +43494,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>8305</v>
+        <v>8333</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2999</t>
+          <t>+3027</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -60,6 +60,7 @@
     <sheet name="2026-09-03" sheetId="51" state="visible" r:id="rId51"/>
     <sheet name="2026-09-04" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="2026-09-05" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="2026-09-06" sheetId="54" state="visible" r:id="rId54"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43556,6 +43557,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-06 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2429</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+840</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>3528</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+2520</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>453</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>410</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+252</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2511</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>443</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>16394</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+7014</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>8631</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+4905</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>14608</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+4716</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>9836</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>4777</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+2634</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>15814</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+7187</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>13103</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+4770</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -43581,7 +43581,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-06 13:01:00</t>
+          <t>Timestamp: 2026-09-06 13:31:00</t>
         </is>
       </c>
     </row>
@@ -44014,11 +44014,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>16394</v>
+        <v>17234</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+7014</t>
+          <t>+7854</t>
         </is>
       </c>
     </row>
@@ -44329,11 +44329,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>15814</v>
+        <v>16150</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+7187</t>
+          <t>+7523</t>
         </is>
       </c>
     </row>
@@ -44374,11 +44374,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>13103</v>
+        <v>13439</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+4770</t>
+          <t>+5106</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -61,6 +61,7 @@
     <sheet name="2026-09-04" sheetId="52" state="visible" r:id="rId52"/>
     <sheet name="2026-09-05" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="2026-09-06" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="2026-09-07" sheetId="55" state="visible" r:id="rId55"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44436,6 +44437,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-07 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>5151</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+2722</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>7056</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+3528</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Izuna</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>503</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+50</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>606</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+196</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2511</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>443</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>23093</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+5859</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>13407</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+4776</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>21263</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+6655</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker LITE</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>14078</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>+4242</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>5622</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+845</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>23992</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+7842</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>20111</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+6672</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>3696</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+3696</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -44461,7 +44461,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-07 13:01:00</t>
+          <t>Timestamp: 2026-09-07 13:31:00</t>
         </is>
       </c>
     </row>
@@ -44894,11 +44894,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>23093</v>
+        <v>23153</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+5859</t>
+          <t>+5919</t>
         </is>
       </c>
     </row>
@@ -44954,11 +44954,11 @@
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>21263</v>
+        <v>21313</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>+6655</t>
+          <t>+6705</t>
         </is>
       </c>
     </row>
@@ -45149,11 +45149,11 @@
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>14078</v>
+        <v>14138</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>+4242</t>
+          <t>+4302</t>
         </is>
       </c>
     </row>
@@ -45209,11 +45209,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>23992</v>
+        <v>24052</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+7842</t>
+          <t>+7902</t>
         </is>
       </c>
     </row>
@@ -45254,11 +45254,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>20111</v>
+        <v>20162</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+6672</t>
+          <t>+6723</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -62,6 +62,7 @@
     <sheet name="2026-09-05" sheetId="53" state="visible" r:id="rId53"/>
     <sheet name="2026-09-06" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="2026-09-07" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="2026-09-08" sheetId="56" state="visible" r:id="rId56"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45316,6 +45317,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-08 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>359</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+70</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>5832</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+681</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>7226</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+170</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>503</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>626</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>MATHEMATRICK</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3126</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+615</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>723</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+280</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>26052</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2899</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>14409</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>23624</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+2311</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Hail AangEX</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>15162</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2260</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+1252</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>5622</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>26775</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2723</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>370</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>22248</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2086</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>5399</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+1703</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -45341,7 +45341,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-08 13:01:00</t>
+          <t>Timestamp: 2026-09-08 13:31:00</t>
         </is>
       </c>
     </row>
@@ -46089,11 +46089,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>26775</v>
+        <v>26835</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2723</t>
+          <t>+2783</t>
         </is>
       </c>
     </row>
@@ -46164,11 +46164,11 @@
         </is>
       </c>
       <c r="B57" s="5" t="n">
-        <v>5399</v>
+        <v>5459</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>+1703</t>
+          <t>+1763</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -63,6 +63,7 @@
     <sheet name="2026-09-06" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="2026-09-07" sheetId="55" state="visible" r:id="rId55"/>
     <sheet name="2026-09-08" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="2026-09-09" sheetId="57" state="visible" r:id="rId57"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46196,6 +46197,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-09 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>+20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>6372</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>9258</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+2032</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>2091</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1588</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>696</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+70</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>ASHBORN™</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>3126</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>28283</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+2231</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>15729</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1320</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>25924</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+2300</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Hail AangEX</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>15162</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>3364</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+1104</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>5622</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>29815</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2980</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>+302</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>25210</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2962</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>7643</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+2184</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -46221,7 +46221,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-09 13:01:00</t>
+          <t>Timestamp: 2026-09-09 13:31:00</t>
         </is>
       </c>
     </row>
@@ -46504,11 +46504,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>2091</v>
+        <v>2151</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>+1588</t>
+          <t>+1648</t>
         </is>
       </c>
     </row>
@@ -46534,11 +46534,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>696</v>
+        <v>996</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>+70</t>
+          <t>+370</t>
         </is>
       </c>
     </row>
@@ -46575,7 +46575,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>ASHBORN™</t>
+          <t>MATHEMATRICK</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
@@ -46583,7 +46583,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -46669,11 +46669,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>15729</v>
+        <v>15789</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>+1320</t>
+          <t>+1380</t>
         </is>
       </c>
     </row>
@@ -46969,11 +46969,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>29815</v>
+        <v>29875</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2980</t>
+          <t>+3040</t>
         </is>
       </c>
     </row>
@@ -47014,11 +47014,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>25210</v>
+        <v>25270</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2962</t>
+          <t>+3022</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -64,6 +64,7 @@
     <sheet name="2026-09-07" sheetId="55" state="visible" r:id="rId55"/>
     <sheet name="2026-09-08" sheetId="56" state="visible" r:id="rId56"/>
     <sheet name="2026-09-09" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="2026-09-10" sheetId="58" state="visible" r:id="rId58"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47076,6 +47077,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-10 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>6672</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>10338</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>3549</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+1398</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1188</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+192</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>C.L.A.Z</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>4197</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1071</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>30227</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1944</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>18015</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+2226</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>27838</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1914</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2271</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1068</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>15162</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>+1164</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>5922</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>32695</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>27040</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1770</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>9983</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+2340</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>484</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -47101,7 +47101,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-10 13:01:00</t>
+          <t>Timestamp: 2026-09-10 13:31:00</t>
         </is>
       </c>
     </row>
@@ -47534,11 +47534,11 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>30227</v>
+        <v>30287</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>+1944</t>
+          <t>+2004</t>
         </is>
       </c>
     </row>
@@ -47549,11 +47549,11 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>18015</v>
+        <v>18075</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>+2226</t>
+          <t>+2286</t>
         </is>
       </c>
     </row>
@@ -47849,11 +47849,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>32695</v>
+        <v>32755</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2880</t>
         </is>
       </c>
     </row>
@@ -47894,11 +47894,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>27040</v>
+        <v>27100</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+1770</t>
+          <t>+1830</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -65,6 +65,7 @@
     <sheet name="2026-09-08" sheetId="56" state="visible" r:id="rId56"/>
     <sheet name="2026-09-09" sheetId="57" state="visible" r:id="rId57"/>
     <sheet name="2026-09-10" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="2026-09-11" sheetId="59" state="visible" r:id="rId59"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -47956,6 +47957,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-11 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>6672</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>+10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1782</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+1782</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>12008</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1670</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+1800</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>1644</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+1644</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>5694</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+2145</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>ProfessorX ?</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1188</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>C.L.A.Z</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>5397</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>32219</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1932</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>19386</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+1311</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>29920</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+2082</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>2631</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+360</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>15162</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>6222</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>35575</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2820</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>28893</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+1793</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>+300</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>484</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -47981,7 +47981,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-11 13:01:00</t>
+          <t>Timestamp: 2026-09-11 13:31:00</t>
         </is>
       </c>
     </row>
@@ -48084,11 +48084,11 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1782</v>
+        <v>1842</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+1782</t>
+          <t>+1842</t>
         </is>
       </c>
     </row>
@@ -48099,11 +48099,11 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>12008</v>
+        <v>12068</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+1670</t>
+          <t>+1730</t>
         </is>
       </c>
     </row>
@@ -48129,11 +48129,11 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>1828</v>
+        <v>1888</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>+1800</t>
+          <t>+1860</t>
         </is>
       </c>
     </row>
@@ -48174,11 +48174,11 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1644</v>
+        <v>1650</v>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>+1644</t>
+          <t>+1650</t>
         </is>
       </c>
     </row>
@@ -48309,11 +48309,11 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+50</t>
         </is>
       </c>
     </row>
@@ -48729,11 +48729,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>35575</v>
+        <v>35635</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2820</t>
+          <t>+2880</t>
         </is>
       </c>
     </row>
@@ -48774,11 +48774,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>28893</v>
+        <v>28953</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+1793</t>
+          <t>+1853</t>
         </is>
       </c>
     </row>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -66,6 +66,7 @@
     <sheet name="2026-09-09" sheetId="57" state="visible" r:id="rId57"/>
     <sheet name="2026-09-10" sheetId="58" state="visible" r:id="rId58"/>
     <sheet name="2026-09-11" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="2026-09-12" sheetId="60" state="visible" r:id="rId60"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49715,6 +49716,885 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Clan: Shad0w Ninja Clan (105)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp: 2026-09-12 13:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Total Reps</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Daily Reps (+1d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>dogan</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>$ p i r i t</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Harimukun</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>NAOR</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>6672</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Yata</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>AangEX</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>2382</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>+540</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Feirisu</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>13808</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>+1740</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>£_Darkz_£</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>AstreaEX</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>4489</v>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>+2601</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Wolf †</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>820</v>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Andrey</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>4194</v>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>+2544</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>BlacKAkiresu O</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>YE Brandy</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Tobi</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ikhram </t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>KOSAKI</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>PRINCE G™</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>5834</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>+140</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Yhwach Genryusai</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>MeiMei</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>1228</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NicolasRicko</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Izx Hatake Jr</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>C.L.A.Z</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Devia Ayu</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6474</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>+1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>~[AnbuDream]~</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Ryujin Senju™</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heisenberg </t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Tobirama Senju™</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>33710</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>+1491</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>ZenithEX</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>19890</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>+504</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>§åñÐåïmårµ | Frtners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>MERU™</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Vnzla Anbu |SN</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>31261</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>+1341</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SNC | Signature</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Fusion</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Sesshomaru</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>KYO</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nitro </t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>SL41F3RT</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>King Fortuners</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>3633</v>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>+1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Raiden</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>ShadowRavenX</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>420</v>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Aldrin</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>SNC | TemperiTa</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>SmallDino</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Breaker</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>15162</v>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Kokyotosu</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>4528</v>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Arya</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Stüssy</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>6322</v>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>+100</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Jonny Brown</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>37965</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>+2330</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Knightwalker</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>672</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">a fucking ninja </t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Aiah</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>31584</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>+2631</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>[R23] Cub †</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Izx Infernity </t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>10283</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Erza Scarlet</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>1084</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>+600</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/clan_105.xlsx
+++ b/clan_105.xlsx
@@ -49740,7 +49740,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Timestamp: 2026-09-12 13:01:00</t>
+          <t>Timestamp: 2026-09-12 13:31:00</t>
         </is>
       </c>
     </row>
@@ -50488,11 +50488,11 @@
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>37965</v>
+        <v>38085</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>+2330</t>
+          <t>+2450</t>
         </is>
       </c>
     </row>
@@ -50533,11 +50533,11 @@
         </is>
       </c>
       <c r="B55" s="5" t="n">
-        <v>31584</v>
+        <v>31685</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>+2631</t>
+          <t>+2732</t>
         </is>
       </c>
     </row>
